--- a/iba/docs/escalation actions worksheet.xlsx
+++ b/iba/docs/escalation actions worksheet.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="1" min="1" max="2"/>
@@ -1969,6 +1969,16 @@
           <t>-ResolutionKind</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-NextAction</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>-SupersededBy</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="F39" t="inlineStr">
@@ -1983,7 +1993,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>touched|narrowed|forward|ruling|note|closed|reopened</t>
+          <t>touched|narrowed|forward|ruling|note|closed|reopened|withdrawn|superseded (superseded names OT-nn[.n] or #nnnn in -Respond)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2049,6 +2059,16 @@
       <c r="W39" t="inlineStr">
         <is>
           <t>SelfCorrectable (threads, T4)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>reject (with -State withdraw|supersede) to end a thread</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>supersede only: the successor thread OT-nn (open items move to it)</t>
         </is>
       </c>
     </row>
@@ -2415,6 +2435,195 @@
       <c r="V49" t="inlineStr">
         <is>
           <t>thread</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>withdraw an item</t>
+        </is>
+      </c>
+      <c r="C50">
+        <f>D50&amp;" "&amp;$E$38&amp;" "&amp;E50&amp;" "&amp;$F$38&amp;" "&amp;F50&amp;" "&amp;$G$38&amp;" "&amp;G50&amp;" "&amp;$H$38&amp;" "&amp;H50&amp;" "&amp;$I$38&amp;" '"&amp;I50&amp;"'"&amp;" "&amp;$R$38&amp;" "&amp;R50</f>
+        <v/>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Escalation.ps1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OT-16</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>OT-16.3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>withdrawn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>no longer relevant: the ruling of 2026-10-12</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>supersede an item</t>
+        </is>
+      </c>
+      <c r="C51">
+        <f>D51&amp;" "&amp;$E$38&amp;" "&amp;E51&amp;" "&amp;$F$38&amp;" "&amp;F51&amp;" "&amp;$G$38&amp;" "&amp;G51&amp;" "&amp;$H$38&amp;" "&amp;H51&amp;" "&amp;$I$38&amp;" '"&amp;I51&amp;"'"&amp;" "&amp;$R$38&amp;" "&amp;R51</f>
+        <v/>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Escalation.ps1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>OT-16</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>OT-16.3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>carried by OT-41.2: the same question, wider</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>withdraw a thread</t>
+        </is>
+      </c>
+      <c r="C52">
+        <f>D52&amp;" "&amp;$E$38&amp;" "&amp;E52&amp;" "&amp;$F$38&amp;" "&amp;F52&amp;" "&amp;$X$38&amp;" "&amp;X52&amp;" "&amp;$S$38&amp;" "&amp;S52&amp;" "&amp;$U$38&amp;" '"&amp;U52&amp;"'"&amp;" "&amp;$R$38&amp;" "&amp;R52</f>
+        <v/>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Escalation.ps1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>OT-40</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>no longer relevant</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>supersede a thread</t>
+        </is>
+      </c>
+      <c r="C53">
+        <f>D53&amp;" "&amp;$E$38&amp;" "&amp;E53&amp;" "&amp;$F$38&amp;" "&amp;F53&amp;" "&amp;$X$38&amp;" "&amp;X53&amp;" "&amp;$S$38&amp;" "&amp;S53&amp;" "&amp;$Y$38&amp;" "&amp;Y53&amp;" "&amp;$U$38&amp;" '"&amp;U53&amp;"'"&amp;" "&amp;$R$38&amp;" "&amp;R53</f>
+        <v/>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Escalation.ps1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>OT-40</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>supersede</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>OT-41 carries the same question</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>OT-41</t>
         </is>
       </c>
     </row>
